--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_d_enveje_a_2019_valparaiso.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_d_enveje_a_2019_valparaiso.xlsx
@@ -120,7 +120,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 14:05</t>
+    <t xml:space="preserve">2026-09-24 00:56</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -558,13 +558,13 @@
         <v>38</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>-0.22</v>
+        <v>-0.23</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>-0.09</v>
+        <v>-0.08</v>
       </c>
     </row>
     <row r="3">
@@ -575,19 +575,19 @@
         <v>8</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>-0.49</v>
+        <v>-0.48</v>
       </c>
       <c r="D3" s="2" t="n">
         <v>38</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>-0.29</v>
+        <v>-0.3</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>-0.19</v>
+        <v>-0.18</v>
       </c>
     </row>
     <row r="4">
@@ -607,7 +607,7 @@
         <v>-0.14</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="G4" s="2" t="n">
         <v>-0.34</v>
@@ -630,10 +630,10 @@
         <v>0.24</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
     </row>
     <row r="6">
@@ -644,7 +644,7 @@
         <v>8</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="D6" s="2" t="n">
         <v>38</v>
@@ -653,10 +653,10 @@
         <v>0.33</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>-0.1</v>
+        <v>-0.11</v>
       </c>
     </row>
     <row r="7">
@@ -673,13 +673,13 @@
         <v>38</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>0.02</v>
+        <v>0.04</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>-0.22</v>
+        <v>-0.24</v>
       </c>
     </row>
     <row r="8">
@@ -696,13 +696,13 @@
         <v>38</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>-0.18</v>
+        <v>-0.16</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="9">
@@ -719,13 +719,13 @@
         <v>38</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>-0.2</v>
+        <v>-0.18</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
     </row>
     <row r="10">
@@ -736,19 +736,19 @@
         <v>14</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>-0.21</v>
+        <v>-0.22</v>
       </c>
       <c r="D10" s="2" t="n">
         <v>37</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>-0.08</v>
+        <v>-0.06</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>-0.14</v>
+        <v>-0.15</v>
       </c>
     </row>
     <row r="11">
@@ -765,13 +765,13 @@
         <v>37</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>-0.08</v>
+        <v>-0.07</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>-0.14</v>
+        <v>-0.15</v>
       </c>
     </row>
     <row r="12">
@@ -791,7 +791,7 @@
         <v>0.16</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="G12" s="2" t="n">
         <v>-0.68</v>
@@ -811,13 +811,13 @@
         <v>38</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>-0.62</v>
+        <v>-0.63</v>
       </c>
     </row>
     <row r="14">
@@ -834,13 +834,13 @@
         <v>38</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>0.19</v>
+        <v>0.21</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>-0.22</v>
+        <v>-0.24</v>
       </c>
     </row>
     <row r="15">
@@ -860,10 +860,10 @@
         <v>-0.12</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
     </row>
     <row r="16">
@@ -874,19 +874,19 @@
         <v>14</v>
       </c>
       <c r="C16" s="2" t="n">
-        <v>0.06</v>
+        <v>0.07</v>
       </c>
       <c r="D16" s="2" t="n">
         <v>37</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>0.13</v>
+        <v>0.15</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>-0.07</v>
+        <v>-0.08</v>
       </c>
     </row>
     <row r="17">
@@ -903,10 +903,10 @@
         <v>37</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="G17" s="2" t="n">
         <v>-0.02</v>
@@ -920,19 +920,19 @@
         <v>26</v>
       </c>
       <c r="C18" s="2" t="n">
-        <v>-0.58</v>
+        <v>-0.57</v>
       </c>
       <c r="D18" s="2" t="n">
         <v>38</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>-0.39</v>
+        <v>-0.4</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>-0.18</v>
+        <v>-0.17</v>
       </c>
     </row>
     <row r="19">
@@ -949,10 +949,10 @@
         <v>38</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>-0.04</v>
+        <v>-0.05</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="G19" s="2" t="n">
         <v>0.36</v>
@@ -966,19 +966,19 @@
         <v>28</v>
       </c>
       <c r="C20" s="2" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="D20" s="2" t="n">
+        <v>38</v>
+      </c>
+      <c r="E20" s="2" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="F20" s="2" t="n">
+        <v>346</v>
+      </c>
+      <c r="G20" s="2" t="n">
         <v>0.23</v>
-      </c>
-      <c r="D20" s="2" t="n">
-        <v>38</v>
-      </c>
-      <c r="E20" s="2" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="F20" s="2" t="n">
-        <v>343</v>
-      </c>
-      <c r="G20" s="2" t="n">
-        <v>0.22</v>
       </c>
     </row>
     <row r="21">
@@ -995,13 +995,13 @@
         <v>38</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_d_enveje_a_2019_valparaiso.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_d_enveje_a_2019_valparaiso.xlsx
@@ -105,7 +105,7 @@
     <t xml:space="preserve">Migración</t>
   </si>
   <si>
-    <t xml:space="preserve">Movilidad interna (CMI)</t>
+    <t xml:space="preserve">Movilidad interna comunal (CMI)</t>
   </si>
   <si>
     <t xml:space="preserve">Saldo migratorio</t>
@@ -120,7 +120,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-24 00:56</t>
+    <t xml:space="preserve">2026-10-01 23:21</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_d_enveje_a_2019_valparaiso.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_d_enveje_a_2019_valparaiso.xlsx
@@ -120,7 +120,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-01 23:21</t>
+    <t xml:space="preserve">2026-10-05 19:37</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
